--- a/multi_regression/results_n_10_m_100_d_1000/figs_100/regression_result.xlsx
+++ b/multi_regression/results_n_10_m_100_d_1000/figs_100/regression_result.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.3145 $\pm$ 0.0197</t>
+          <t>0.3332 $\pm$ 0.0291</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.3145 $\pm$ 0.0197</t>
+          <t>0.3333 $\pm$ 0.0294</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.3145 $\pm$ 0.0197</t>
+          <t>0.3335 $\pm$ 0.0292</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.3145 $\pm$ 0.0197</t>
+          <t>0.3334 $\pm$ 0.0294</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18.2150 $\pm$ 4.1086</t>
+          <t>19.9742 $\pm$ 6.6203</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.7200 $\pm$ 4.6819</t>
+          <t>41.2616 $\pm$ 6.9060</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29.9402 $\pm$ 6.7799</t>
+          <t>32.0460 $\pm$ 10.0458</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.8209 $\pm$ 5.5944</t>
+          <t>26.8068 $\pm$ 8.5594</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>317068.1149 $\pm$ 284379.3910</t>
+          <t>238508.1541 $\pm$ 226443.5438</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>159729.1394 $\pm$ 110564.0902</t>
+          <t>189992.9754 $\pm$ 133164.3801</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>156361.4454 $\pm$ 90931.0217</t>
+          <t>291508.6538 $\pm$ 134315.1476</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>278210.2467 $\pm$ 208072.4886</t>
+          <t>475231.1347 $\pm$ 319930.1804</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>281066.0421 $\pm$ 367694.1271</t>
+          <t>320323.8298 $\pm$ 167982.3909</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>208938.6957 $\pm$ 168747.9588</t>
+          <t>168988.7222 $\pm$ 133829.4707</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>145083.0105 $\pm$ 89103.3081</t>
+          <t>211325.0381 $\pm$ 148603.5107</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>165022.3408 $\pm$ 210824.2153</t>
+          <t>320956.9300 $\pm$ 253180.8916</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>140385.3602 $\pm$ 154164.4938</t>
+          <t>1260.2859 $\pm$ 432.7142</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>136951.0156 $\pm$ 103665.8081</t>
+          <t>689.7441 $\pm$ 182.8318</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>128454.6879 $\pm$ 126967.3898</t>
+          <t>1033.9237 $\pm$ 272.2435</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>157112.7505 $\pm$ 155356.0183</t>
+          <t>1161.9225 $\pm$ 357.0491</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>179.1323 $\pm$ 66.1070</t>
+          <t>566429.5256 $\pm$ 405288.8450</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>133.8253 $\pm$ 40.2935</t>
+          <t>281327.1374 $\pm$ 194961.8628</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>194.8157 $\pm$ 87.7046</t>
+          <t>275343.6517 $\pm$ 140822.9682</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>207.2781 $\pm$ 87.6148</t>
+          <t>227649.8785 $\pm$ 201093.3582</t>
         </is>
       </c>
     </row>
